--- a/Pokedex/SHINYDEX_workspace/ShinyDex_2.0/Shiny_Dex_Out.xlsx
+++ b/Pokedex/SHINYDEX_workspace/ShinyDex_2.0/Shiny_Dex_Out.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aiaqu\git_clones\Projects\Pokedex\SHINYDEX_workspace\ShinyDex_2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A7FA98-E36E-4575-9EFC-E40EA67D4F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEAD99A0-323A-44BC-AA2D-86ECBCB279D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="shiny_dex" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2540" uniqueCount="785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2531" uniqueCount="784">
   <si>
     <t>entryNo</t>
   </si>
@@ -2372,9 +2372,6 @@
   </si>
   <si>
     <t>Vivillon</t>
-  </si>
-  <si>
-    <t>Looloo</t>
   </si>
 </sst>
 </file>
@@ -2741,8 +2738,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P327"/>
+  <dimension ref="A1:P326"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -13500,41 +13500,6 @@
         <v>97</v>
       </c>
       <c r="P326" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="327" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A327">
-        <v>325</v>
-      </c>
-      <c r="B327">
-        <v>134</v>
-      </c>
-      <c r="C327" t="s">
-        <v>784</v>
-      </c>
-      <c r="F327" t="s">
-        <v>45</v>
-      </c>
-      <c r="G327" t="s">
-        <v>17</v>
-      </c>
-      <c r="H327" t="s">
-        <v>780</v>
-      </c>
-      <c r="I327" t="s">
-        <v>229</v>
-      </c>
-      <c r="J327" t="s">
-        <v>19</v>
-      </c>
-      <c r="L327" t="s">
-        <v>96</v>
-      </c>
-      <c r="M327" t="s">
-        <v>97</v>
-      </c>
-      <c r="P327" t="s">
         <v>21</v>
       </c>
     </row>
